--- a/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 1,26</t>
+          <t>-5,47; 1,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,25</t>
+          <t>-3,09; 3,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 1,34</t>
+          <t>-7,3; 0,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 4,84</t>
+          <t>-3,26; 4,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,03</t>
+          <t>-4,76; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,79</t>
+          <t>-5,66; 4,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,58</t>
+          <t>-3,2; 1,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,91</t>
+          <t>-3,07; 2,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,95</t>
+          <t>-5,87; 0,8</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 23,61</t>
+          <t>-59,3; 21,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 72,84</t>
+          <t>-35,93; 67,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 30,16</t>
+          <t>-85,62; 25,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 76,6</t>
+          <t>-30,67; 71,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,0; 28,94</t>
+          <t>-49,78; 36,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 74,91</t>
+          <t>-58,03; 70,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,31; 24,45</t>
+          <t>-34,86; 25,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 29,85</t>
+          <t>-34,41; 31,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 15,55</t>
+          <t>-66,55; 11,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 0,82</t>
+          <t>-4,18; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,08</t>
+          <t>-2,95; 2,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; -2,83</t>
+          <t>-7,41; -2,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 5,48</t>
+          <t>-1,23; 5,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,31</t>
+          <t>-5,25; 0,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -3,45</t>
+          <t>-8,67; -3,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,31</t>
+          <t>-2,23; 2,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,01</t>
+          <t>-3,12; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -4,13</t>
+          <t>-7,24; -3,85</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,38; 19,69</t>
+          <t>-56,52; 21,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,87; 61,67</t>
+          <t>-37,31; 59,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-98,35; -37,1</t>
+          <t>-98,76; -31,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,3; 87,57</t>
+          <t>-13,22; 85,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 8,99</t>
+          <t>-56,1; 5,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,76; -53,16</t>
+          <t>-91,39; -51,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 40,91</t>
+          <t>-26,56; 36,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,24; 17,79</t>
+          <t>-38,44; 17,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,86; -61,21</t>
+          <t>-89,7; -60,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,96</t>
+          <t>1,08; 6,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,72</t>
+          <t>-2,24; 2,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,65</t>
+          <t>-2,42; 2,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,45</t>
+          <t>-0,99; 5,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,36</t>
+          <t>-4,26; 1,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; -0,63</t>
+          <t>-6,19; -0,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,7</t>
+          <t>0,63; 4,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,35</t>
+          <t>-2,59; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,02</t>
+          <t>-3,6; 0,28</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,02; 212,28</t>
+          <t>18,05; 206,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 104,16</t>
+          <t>-40,49; 93,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,56; 87,02</t>
+          <t>-46,32; 85,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 83,72</t>
+          <t>-10,4; 81,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 21,18</t>
+          <t>-43,27; 22,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,08; -8,69</t>
+          <t>-61,42; -7,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,94; 89,15</t>
+          <t>7,66; 92,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 25,54</t>
+          <t>-35,19; 26,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 1,17</t>
+          <t>-50,83; 5,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,01</t>
+          <t>-2,01; 2,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 2,33</t>
+          <t>-2,66; 2,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,05</t>
+          <t>-4,23; 0,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,8</t>
+          <t>-3,73; 1,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 1,48</t>
+          <t>-3,42; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -0,32</t>
+          <t>-4,61; -0,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,49</t>
+          <t>-2,05; 1,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,19</t>
+          <t>-2,27; 1,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; -0,68</t>
+          <t>-3,79; -0,65</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 120,35</t>
+          <t>-39,99; 109,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 89,92</t>
+          <t>-51,2; 95,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 4,16</t>
+          <t>-80,69; 5,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 60,11</t>
+          <t>-57,17; 45,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 43,91</t>
+          <t>-52,45; 44,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,63; -6,25</t>
+          <t>-69,66; -3,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 42,91</t>
+          <t>-37,16; 41,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,79; 35,72</t>
+          <t>-42,55; 38,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-71,57; -19,46</t>
+          <t>-72,07; -18,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,62</t>
+          <t>-3,47; 1,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,74</t>
+          <t>-4,11; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,23</t>
+          <t>-4,57; 0,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,35</t>
+          <t>-3,8; 1,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,7</t>
+          <t>-3,74; 1,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -1,11</t>
+          <t>-5,53; -0,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,73</t>
+          <t>-2,81; 0,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 0,26</t>
+          <t>-3,14; 0,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,35; -1,07</t>
+          <t>-4,25; -1,07</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,72; 73,26</t>
+          <t>-65,1; 68,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,06; 34,1</t>
+          <t>-77,26; 44,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 13,23</t>
+          <t>-78,61; 15,75</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 54,96</t>
+          <t>-68,49; 51,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 63,16</t>
+          <t>-64,73; 71,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,26; -39,37</t>
+          <t>-86,31; -31,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-57,23; 25,23</t>
+          <t>-56,11; 20,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 9,96</t>
+          <t>-61,57; 19,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-78,33; -32,5</t>
+          <t>-77,87; -32,57</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,9</t>
+          <t>-2,44; 3,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,83</t>
+          <t>-3,97; 1,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,95</t>
+          <t>-3,97; 0,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,56</t>
+          <t>-2,92; 0,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,83</t>
+          <t>-1,41; 2,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -0,17</t>
+          <t>-3,7; -0,25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,04</t>
+          <t>-2,04; 1,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,54</t>
+          <t>-1,95; 1,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,98; -0,23</t>
+          <t>-3,12; -0,25</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 148,32</t>
+          <t>-55,19; 167,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-85,49; 61,95</t>
+          <t>-81,76; 79,5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 59,31</t>
+          <t>-76,19; 58,54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 111,89</t>
+          <t>-100,0; 114,62</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-64,17; 287,79</t>
+          <t>-57,77; 316,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-95,83; -14,06</t>
+          <t>-96,6; -13,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,58; 59,09</t>
+          <t>-60,85; 66,09</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 92,14</t>
+          <t>-59,52; 71,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-82,73; -10,94</t>
+          <t>-83,11; -13,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,65</t>
+          <t>-2,52; 2,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,8</t>
+          <t>-3,06; 1,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,69</t>
+          <t>-3,78; 0,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,31</t>
+          <t>-2,93; 1,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 1,62</t>
+          <t>-2,77; 1,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -0,3</t>
+          <t>-3,67; -0,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 1,23</t>
+          <t>-2,07; 1,13</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,11</t>
+          <t>-2,1; 1,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,35</t>
+          <t>-3,07; -0,31</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 333,72</t>
+          <t>-79,68; 398,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 249,56</t>
+          <t>-88,82; 262,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-91,31; 181,64</t>
+          <t>-92,35; 164,75</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-87,47; 144,62</t>
+          <t>-83,74; 242,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 298,7</t>
+          <t>-84,28; 421,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 16,3</t>
+          <t>-100,0; 4,09</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-66,24; 112,29</t>
+          <t>-70,49; 94,29</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,99; 128,08</t>
+          <t>-73,78; 115,5</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,39; -16,12</t>
+          <t>-90,71; -6,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,0</t>
+          <t>-1,14; 1,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,51</t>
+          <t>-1,57; 0,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,56; -1,52</t>
+          <t>-3,59; -1,57</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,47</t>
+          <t>-0,96; 1,3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,34</t>
+          <t>-2,47; -0,27</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -2,45</t>
+          <t>-4,59; -2,45</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,88</t>
+          <t>-0,72; 0,88</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,7; -0,2</t>
+          <t>-1,77; -0,24</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -2,27</t>
+          <t>-3,76; -2,31</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 23,47</t>
+          <t>-20,63; 24,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 11,96</t>
+          <t>-29,48; 14,64</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,75; -33,6</t>
+          <t>-67,27; -36,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 27,22</t>
+          <t>-14,14; 24,01</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-39,62; -5,81</t>
+          <t>-38,07; -4,82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-68,98; -44,91</t>
+          <t>-69,3; -45,29</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 17,79</t>
+          <t>-12,29; 17,9</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,5; -3,99</t>
+          <t>-30,23; -4,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-64,78; -45,72</t>
+          <t>-65,2; -45,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-4,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,14</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,78</t>
+          <t>-2,7</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,03</t>
+          <t>-5,28; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,81</t>
+          <t>-3,22; 4,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,87</t>
+          <t>-7,28; -0,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 4,94</t>
+          <t>-2,7; 4,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 2,37</t>
+          <t>-5,27; 2,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 4,59</t>
+          <t>-5,04; 4,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,68</t>
+          <t>-3,0; 1,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 2,08</t>
+          <t>-3,03; 2,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,8</t>
+          <t>-5,42; 0,36</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-54,9%</t>
+          <t>-57,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-13,52%</t>
+          <t>-11,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-35,46%</t>
+          <t>-34,39%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 21,74</t>
+          <t>-60,11; 19,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 67,85</t>
+          <t>-36,79; 68,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,62; 25,65</t>
+          <t>-85,54; 4,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 71,76</t>
+          <t>-27,25; 72,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,78; 36,92</t>
+          <t>-50,7; 29,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,03; 70,29</t>
+          <t>-53,31; 62,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,86; 25,32</t>
+          <t>-33,6; 29,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 31,47</t>
+          <t>-34,84; 31,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 11,49</t>
+          <t>-61,11; 6,82</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-4,88</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,1</t>
+          <t>-5,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,58</t>
+          <t>-4,88</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,08</t>
+          <t>-3,99; 1,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 2,87</t>
+          <t>-2,58; 2,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; -2,69</t>
+          <t>-7,0; -2,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,17</t>
+          <t>-1,24; 5,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,28</t>
+          <t>-5,2; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,67; -3,65</t>
+          <t>-7,96; -2,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,12</t>
+          <t>-1,89; 2,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,0</t>
+          <t>-2,87; 1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,24; -3,85</t>
+          <t>-6,82; -3,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-84,82%</t>
+          <t>-78,55%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-78,09%</t>
+          <t>-64,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-80,39%</t>
+          <t>-70,33%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,52; 21,51</t>
+          <t>-51,64; 23,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,31; 59,34</t>
+          <t>-35,92; 59,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-98,76; -31,36</t>
+          <t>-92,75; -37,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,22; 85,77</t>
+          <t>-13,86; 87,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,1; 5,42</t>
+          <t>-55,58; 11,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-91,39; -51,31</t>
+          <t>-82,34; -37,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 36,81</t>
+          <t>-23,9; 37,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 17,9</t>
+          <t>-37,03; 22,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,7; -60,1</t>
+          <t>-83,41; -50,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,33</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-0,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,2</t>
+          <t>1,3; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,64</t>
+          <t>-2,07; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,5</t>
+          <t>-1,66; 3,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 5,42</t>
+          <t>-0,98; 5,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,44</t>
+          <t>-4,2; 1,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -0,63</t>
+          <t>-4,2; 1,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,84</t>
+          <t>0,93; 4,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,39</t>
+          <t>-2,56; 1,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,28</t>
+          <t>-2,21; 1,6</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-39,94%</t>
+          <t>-16,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-27,29%</t>
+          <t>-4,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18,05; 206,39</t>
+          <t>19,37; 223,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 93,83</t>
+          <t>-37,3; 104,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,32; 85,55</t>
+          <t>-31,41; 116,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 81,37</t>
+          <t>-10,15; 82,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 22,87</t>
+          <t>-42,18; 24,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,42; -7,61</t>
+          <t>-41,51; 24,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 92,48</t>
+          <t>12,11; 92,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 26,0</t>
+          <t>-35,33; 21,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,83; 5,08</t>
+          <t>-30,5; 29,26</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,87</t>
+          <t>-0,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-1,25</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,93</t>
+          <t>-1,63; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,53</t>
+          <t>-2,77; 2,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 0,16</t>
+          <t>-2,8; 1,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 1,49</t>
+          <t>-3,54; 1,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,53</t>
+          <t>-3,38; 1,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,21</t>
+          <t>-4,12; 0,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,49</t>
+          <t>-2,04; 1,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,32</t>
+          <t>-2,23; 1,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,65</t>
+          <t>-2,93; 0,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-47,92%</t>
+          <t>-16,79%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-46,98%</t>
+          <t>-37,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-48,13%</t>
+          <t>-28,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 109,45</t>
+          <t>-34,24; 117,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-51,2; 95,94</t>
+          <t>-52,03; 89,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-80,69; 5,11</t>
+          <t>-55,46; 57,02</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,17; 45,14</t>
+          <t>-56,33; 46,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,45; 44,74</t>
+          <t>-54,12; 45,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,66; -3,98</t>
+          <t>-60,62; 12,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,16; 41,29</t>
+          <t>-37,39; 46,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 38,39</t>
+          <t>-41,15; 34,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,07; -18,66</t>
+          <t>-51,89; 9,07</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,02</t>
+          <t>-1,87</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-2,86</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-2,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 1,61</t>
+          <t>-3,28; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,88</t>
+          <t>-4,32; 0,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 0,09</t>
+          <t>-4,14; 0,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,29</t>
+          <t>-3,92; 1,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,75</t>
+          <t>-3,61; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,53; -0,99</t>
+          <t>-5,33; -0,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,51</t>
+          <t>-2,92; 0,7</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,55</t>
+          <t>-3,25; 0,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,25; -1,07</t>
+          <t>-4,11; -0,94</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-50,55%</t>
+          <t>-46,83%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-69,68%</t>
+          <t>-68,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-60,2%</t>
+          <t>-57,98%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,1; 68,44</t>
+          <t>-64,45; 92,24</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,26; 44,32</t>
+          <t>-77,85; 43,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,61; 15,75</t>
+          <t>-75,71; 18,69</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-68,49; 51,64</t>
+          <t>-66,91; 43,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-64,73; 71,8</t>
+          <t>-64,05; 70,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,31; -31,48</t>
+          <t>-85,95; -32,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-56,11; 20,29</t>
+          <t>-57,99; 23,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-61,57; 19,39</t>
+          <t>-62,31; 11,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-77,87; -32,57</t>
+          <t>-76,51; -28,95</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-1,37</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 3,11</t>
+          <t>-2,74; 2,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,15</t>
+          <t>-4,12; 0,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,86</t>
+          <t>-4,08; 0,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 0,52</t>
+          <t>-3,0; 0,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,96</t>
+          <t>-1,5; 2,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,25</t>
+          <t>-3,1; 0,39</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,08</t>
+          <t>-2,05; 1,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,16</t>
+          <t>-2,1; 1,26</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,12; -0,25</t>
+          <t>-2,69; 0,08</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-39,8%</t>
+          <t>-41,96%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-73,29%</t>
+          <t>-52,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-58,22%</t>
+          <t>-45,55%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 167,42</t>
+          <t>-60,7; 161,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-81,76; 79,5</t>
+          <t>-83,28; 75,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-76,19; 58,54</t>
+          <t>-78,43; 41,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,62</t>
+          <t>-95,37; 106,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,77; 316,49</t>
+          <t>-60,3; 338,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-96,6; -13,08</t>
+          <t>-86,95; 84,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-60,85; 66,09</t>
+          <t>-61,8; 75,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,52; 71,65</t>
+          <t>-62,14; 72,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,11; -13,09</t>
+          <t>-75,66; 8,97</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,15</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,6</t>
+          <t>-2,66; 2,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,85</t>
+          <t>-2,9; 1,8</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,67</t>
+          <t>-3,56; 0,64</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,45</t>
+          <t>-2,73; 1,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,86</t>
+          <t>-3,07; 1,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -0,43</t>
+          <t>-3,91; -0,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,13</t>
+          <t>-1,92; 1,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,19</t>
+          <t>-2,28; 1,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,31</t>
+          <t>-2,86; -0,22</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-54,02%</t>
+          <t>-49,4%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-82,47%</t>
+          <t>-77,58%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-70,89%</t>
+          <t>-66,06%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 398,84</t>
+          <t>-81,19; 364,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-88,82; 262,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-92,35; 164,75</t>
+          <t>-95,13; 103,73</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-83,74; 242,83</t>
+          <t>-83,1; 206,92</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-84,28; 421,37</t>
+          <t>-86,49; 222,24</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,09</t>
+          <t>-100,0; 7,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 94,29</t>
+          <t>-65,52; 136,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-73,78; 115,5</t>
+          <t>-75,44; 98,73</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-90,71; -6,66</t>
+          <t>-89,25; -6,46</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,55</t>
+          <t>-2,07</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,49</t>
+          <t>-2,71</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-3,03</t>
+          <t>-2,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,06</t>
+          <t>-1,11; 0,99</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,57</t>
+          <t>-1,55; 0,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,59; -1,57</t>
+          <t>-3,08; -1,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,3</t>
+          <t>-1,01; 1,46</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; -0,27</t>
+          <t>-2,47; -0,37</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -2,45</t>
+          <t>-3,79; -1,62</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,88</t>
+          <t>-0,66; 0,87</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,24</t>
+          <t>-1,72; -0,18</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,76; -2,31</t>
+          <t>-3,12; -1,68</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-52,91%</t>
+          <t>-42,89%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-58,53%</t>
+          <t>-45,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-56,03%</t>
+          <t>-44,22%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 24,66</t>
+          <t>-20,05; 24,23</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 14,64</t>
+          <t>-28,84; 13,14</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-67,27; -36,86</t>
+          <t>-57,29; -24,51</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 24,01</t>
+          <t>-15,36; 27,51</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-38,07; -4,82</t>
+          <t>-37,97; -7,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-69,3; -45,29</t>
+          <t>-56,91; -30,19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 17,9</t>
+          <t>-11,46; 17,32</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-30,23; -4,76</t>
+          <t>-29,75; -3,53</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,2; -45,67</t>
+          <t>-53,59; -33,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
